--- a/outputs/experiment_summary.xlsx
+++ b/outputs/experiment_summary.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a8007c647b4d44d/Documents/part2_kpi_experiment/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="11_F25DC773A252ABDACC10482F091B54B65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A41BD18-A7D0-4267-AEC3-EA56EA07B7B6}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="11_F25DC773A252ABDACC10482F091B54B65BDE58E5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E909C30-E641-4874-9475-2DDCEBDFD5CD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="experiment_summary" sheetId="1" r:id="rId1"/>
     <sheet name="Region Segment Analysis" sheetId="2" r:id="rId2"/>
     <sheet name="Device Segment Analysis" sheetId="3" r:id="rId3"/>
     <sheet name="Traffic Source Analysis" sheetId="4" r:id="rId4"/>
+    <sheet name="Experiment_sumarry Calculation" sheetId="5" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="44">
   <si>
     <t>Metric</t>
   </si>
@@ -182,7 +183,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -311,13 +312,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -328,92 +326,50 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" pivotButton="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <border>
         <right style="thin">
@@ -738,6 +694,8 @@
     <sheetNames>
       <sheetName val="experiment_data"/>
       <sheetName val="Data_Cleaning_Summary"/>
+      <sheetName val="Hypothesis_Test"/>
+      <sheetName val="GuardRail Metric"/>
       <sheetName val="business_context"/>
     </sheetNames>
     <sheetDataSet>
@@ -41549,11 +41507,17 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -68271,7 +68235,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C9D3E94-4FDD-4F0E-9CD0-D743F84F0C2F}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C9D3E94-4FDD-4F0E-9CD0-D743F84F0C2F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:J10" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField dataField="1" showAll="0"/>
@@ -68377,11 +68341,11 @@
   </colItems>
   <dataFields count="3">
     <dataField name="Count of user_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Average of engagement_score" fld="15" subtotal="average" baseField="3" baseItem="0" numFmtId="168"/>
-    <dataField name="Average of revenue_30d" fld="11" subtotal="average" baseField="3" baseItem="2" numFmtId="168"/>
+    <dataField name="Average of engagement_score" fld="15" subtotal="average" baseField="3" baseItem="0" numFmtId="164"/>
+    <dataField name="Average of revenue_30d" fld="11" subtotal="average" baseField="3" baseItem="2" numFmtId="164"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="48">
+    <format dxfId="34">
       <pivotArea dataOnly="0" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -68390,7 +68354,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -68402,10 +68366,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="32">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="D1" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -68414,7 +68378,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -68426,7 +68390,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="29">
       <pivotArea field="2" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68435,10 +68399,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="28">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="E1" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="27">
       <pivotArea field="2" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68447,10 +68411,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="26">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="F1" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="25">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68459,7 +68423,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="24">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68468,7 +68432,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="23">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68477,23 +68441,23 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="22">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="21">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -68505,7 +68469,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="17">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
   </formats>
@@ -68522,7 +68486,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FDA53BC6-3D1D-444E-8182-7D11BE31BE89}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FDA53BC6-3D1D-444E-8182-7D11BE31BE89}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:J10" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField dataField="1" showAll="0"/>
@@ -68616,11 +68580,11 @@
   </colItems>
   <dataFields count="3">
     <dataField name="Sum of converted_to_paid" fld="10" baseField="4" baseItem="0"/>
-    <dataField name="Average of revenue_30d" fld="11" subtotal="average" baseField="4" baseItem="0" numFmtId="168"/>
+    <dataField name="Average of revenue_30d" fld="11" subtotal="average" baseField="4" baseItem="0" numFmtId="164"/>
     <dataField name="Count of user_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="17">
-    <format dxfId="30">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -68632,10 +68596,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="15">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="D1" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -68644,7 +68608,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -68656,7 +68620,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="12">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -68668,10 +68632,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="11">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="A1" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -68680,7 +68644,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -68692,7 +68656,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="8">
       <pivotArea field="2" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68701,10 +68665,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="7">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="E1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="6">
       <pivotArea field="2" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68713,10 +68677,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="5">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="F1" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="4">
       <pivotArea field="2" grandCol="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68725,10 +68689,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="3">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="G1" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="2">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68737,7 +68701,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="1">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68746,7 +68710,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="0">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -68769,7 +68733,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{067EF41D-032A-4EFF-A7E1-AF42794F8FF7}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{067EF41D-032A-4EFF-A7E1-AF42794F8FF7}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:G12" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField dataField="1" showAll="0"/>
@@ -68865,7 +68829,7 @@
     <dataField name="Sum of converted_to_paid" fld="10" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="7">
+    <format dxfId="42">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -68877,10 +68841,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="41">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" offset="B1" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -68889,7 +68853,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -68901,7 +68865,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -68913,10 +68877,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="37">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -68925,7 +68889,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -69221,164 +69185,142 @@
     <col min="3" max="3" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
-    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
-        <f>COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B3" s="17">
         <v>690</v>
       </c>
-      <c r="C3" s="1">
-        <f>COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C3" s="17">
         <v>710</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$H:$H,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B4" s="17">
         <v>0.63623188405797104</v>
       </c>
-      <c r="C4" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$H:$H,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C4" s="17">
         <v>0.72394366197183102</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$I:$I,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B5" s="17">
         <v>0.25072463768115943</v>
       </c>
-      <c r="C5" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$I:$I,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C5" s="17">
         <v>0.29014084507042254</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$J:$J,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B6" s="17">
         <v>0.15652173913043479</v>
       </c>
-      <c r="C6" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$J:$J,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C6" s="17">
         <v>0.21126760563380281</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$K:$K,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B7" s="17">
         <v>3.1884057971014491E-2</v>
       </c>
-      <c r="C7" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$K:$K,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C7" s="17">
         <v>7.0422535211267609E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
-        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Control")/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B8" s="17">
         <v>51.974318840579706</v>
       </c>
-      <c r="C8" s="1">
-        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Treatment")/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C8" s="17">
         <v>54.254521126760551</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
-        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Control")/COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$K:$K,1)</f>
+      <c r="B9" s="17">
         <v>1630.1036363636363</v>
       </c>
-      <c r="C9" s="1">
-        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Treatment")/COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$K:$K,1)</f>
+      <c r="C9" s="17">
         <v>770.41419999999982</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$N:$N,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B10" s="17">
         <v>0</v>
       </c>
-      <c r="C10" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$N:$N,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C10" s="17">
         <v>4.2253521126760559E-3</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$M:$M,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+      <c r="B11" s="17">
         <v>9.2753623188405798E-2</v>
       </c>
-      <c r="C11" s="1">
-        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$M:$M,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C11" s="17">
         <v>0.16056338028169015</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1">
-        <f>AVERAGEIFS([1]experiment_data!$P:$P,[1]experiment_data!$C:$C,"Control")</f>
+      <c r="B12" s="17">
         <v>57.029532163742729</v>
       </c>
-      <c r="C12" s="1">
-        <f>AVERAGEIFS([1]experiment_data!$P:$P,[1]experiment_data!$C:$C,"Treatment")</f>
+      <c r="C12" s="17">
         <v>62.940028490028489</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1">
-        <f>AVERAGEIFS([1]experiment_data!$O:$O,[1]experiment_data!$C:$C,"Control",[1]experiment_data!$K:$K,1)</f>
+      <c r="B13" s="17">
         <v>8.8636363636363633</v>
       </c>
-      <c r="C13" s="1">
-        <f>AVERAGEIFS([1]experiment_data!$O:$O,[1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$K:$K,1)</f>
+      <c r="C13" s="17">
         <v>6.4</v>
       </c>
     </row>
@@ -69408,44 +69350,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="D3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
+      <c r="D4" s="8"/>
       <c r="E4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="10" t="s">
         <v>24</v>
       </c>
       <c r="J4" t="s">
@@ -69453,7 +69394,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
@@ -69462,7 +69403,7 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E5" t="s">
@@ -69471,174 +69412,174 @@
       <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6">
         <v>201</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="7">
         <v>57.616666666666653</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="9">
         <v>84.500099502487558</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6">
         <v>180</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="7">
         <v>63.153977272727246</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="9">
         <v>80.967500000000001</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="10">
         <v>381</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="11">
         <v>60.222459893048118</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="7">
         <v>82.831154855643064</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7">
         <v>184</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="7">
         <v>56.904972375690591</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="9">
         <v>76.033097826086959</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7">
         <v>183</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="7">
         <v>62.113259668508299</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="9">
         <v>47.25852459016393</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="10">
         <v>367</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="11">
         <v>59.509116022099477</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="7">
         <v>61.685013623978186</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8">
         <v>157</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="7">
         <v>56.556050955414022</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="9">
         <v>18.231464968152867</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8">
         <v>170</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="7">
         <v>63.307692307692328</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="9">
         <v>47.051764705882356</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="10">
         <v>327</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="11">
         <v>60.056134969325186</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="7">
         <v>33.214495412844038</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9">
         <v>148</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="7">
         <v>56.898648648648638</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="9">
         <v>13.684662162162162</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9">
         <v>177</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="7">
         <v>63.223295454545472</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="9">
         <v>41.239830508474583</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="10">
         <v>325</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="11">
         <v>60.334259259259234</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="7">
         <v>28.691630769230766</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10">
         <v>690</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="7">
         <v>57.029532163742751</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="9">
         <v>51.974318840579706</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10">
         <v>710</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="7">
         <v>62.940028490028524</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="9">
         <v>54.254521126760565</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="10">
         <v>1400</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="11">
         <v>60.023160173160178</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="7">
         <v>53.130707142857133</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
+      <c r="A13" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -69669,34 +69610,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="22" t="s">
+      <c r="D3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="25" t="s">
         <v>36</v>
       </c>
     </row>
@@ -69704,25 +69645,25 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="12"/>
+      <c r="D4" s="8"/>
       <c r="E4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="8"/>
+      <c r="H4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
@@ -69731,7 +69672,7 @@
       <c r="C5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E5" t="s">
@@ -69740,204 +69681,204 @@
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6">
         <v>9</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="7">
         <v>84.942949999999996</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="8">
         <v>200</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6">
         <v>14</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="7">
         <v>41.15042253521127</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="8">
         <v>213</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="10">
         <v>23</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="11">
         <v>62.357457627118634</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="10">
         <v>413</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","device_type","Desktop")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","device_type","Desktop")</f>
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","device_type","Desktop")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","device_type","Desktop")</f>
         <v>6.5727699530516437E-2</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>11</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="7">
         <v>42.044436619718304</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="8">
         <v>426</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7">
         <v>32</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="7">
         <v>59.373055555555553</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="8">
         <v>432</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="10">
         <v>43</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="11">
         <v>50.769335664335664</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="10">
         <v>858</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","device_type","Mobile")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","device_type","Mobile")</f>
         <v>2.5821596244131457E-2</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","device_type","Mobile")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","device_type","Mobile")</f>
         <v>7.407407407407407E-2</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="7">
         <v>7.4434545454545455</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="8">
         <v>55</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="7">
         <v>73.330535714285716</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="8">
         <v>56</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="10">
         <v>5</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="11">
         <v>40.683783783783781</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="10">
         <v>111</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","device_type","Tablet")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","device_type","Tablet")</f>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","device_type","Tablet")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","device_type","Tablet")</f>
         <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="7">
         <v>61.485555555555557</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="8">
         <v>9</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="7">
         <v>0</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="8">
         <v>9</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="10">
         <v>1</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="11">
         <v>30.742777777777778</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="10">
         <v>18</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","device_type","Unknown")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","device_type","Unknown")</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","device_type","Unknown")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","device_type","Unknown")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10">
         <v>22</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="7">
         <v>51.974318840579706</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="8">
         <v>690</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10">
         <v>50</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="7">
         <v>54.254521126760572</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="8">
         <v>710</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="10">
         <v>72</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="11">
         <v>53.130707142857133</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="10">
         <v>1400</v>
       </c>
     </row>
@@ -69968,28 +69909,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="H3" s="26" t="s">
+      <c r="C3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="H3" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="21" t="s">
         <v>36</v>
       </c>
     </row>
@@ -69997,248 +69938,248 @@
       <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="8"/>
       <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="12"/>
+      <c r="E4" s="8"/>
       <c r="F4" t="s">
         <v>23</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="25"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="21"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="25"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="21"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6">
         <v>73</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="8">
         <v>2</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6">
         <v>56</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="8">
         <v>4</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6">
         <v>129</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="15">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","traffic_source","Email")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","traffic_source","Email")</f>
         <v>2.7397260273972601E-2</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","traffic_source","Email")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","traffic_source","Email")</f>
         <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>246</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="8">
         <v>5</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7">
         <v>237</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="8">
         <v>15</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7">
         <v>483</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7">
         <v>20</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="15">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","traffic_source","Organic")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","traffic_source","Organic")</f>
         <v>2.032520325203252E-2</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","traffic_source","Organic")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","traffic_source","Organic")</f>
         <v>6.3291139240506333E-2</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>155</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="8">
         <v>2</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8">
         <v>176</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="8">
         <v>11</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8">
         <v>331</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8">
         <v>13</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="15">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","traffic_source","Paid Search")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","traffic_source","Paid Search")</f>
         <v>1.2903225806451613E-2</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","traffic_source","Paid Search")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","traffic_source","Paid Search")</f>
         <v>6.25E-2</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>81</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="8">
         <v>2</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9">
         <v>91</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="8">
         <v>10</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9">
         <v>172</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9">
         <v>12</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="15">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","traffic_source","Referral")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","traffic_source","Referral")</f>
         <v>2.4691358024691357E-2</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","traffic_source","Referral")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","traffic_source","Referral")</f>
         <v>0.10989010989010989</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10">
         <v>129</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="8">
         <v>10</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10">
         <v>132</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="8">
         <v>8</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10">
         <v>261</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10">
         <v>18</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="15">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","traffic_source","Social")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","traffic_source","Social")</f>
         <v>7.7519379844961239E-2</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","traffic_source","Social")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","traffic_source","Social")</f>
         <v>6.0606060606060608E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="8">
         <v>1</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11">
         <v>18</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="8">
         <v>2</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11">
         <v>24</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11">
         <v>3</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="15">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Control","traffic_source","Unknown")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Control","traffic_source","Unknown")</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="14">
         <f>GETPIVOTDATA("Sum of converted_to_paid",$A$3,"experiment_group","Treatment","traffic_source","Unknown")/GETPIVOTDATA("Count of user_id",$A$3,"experiment_group","Treatment","traffic_source","Unknown")</f>
         <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12">
         <v>690</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="8">
         <v>22</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12">
         <v>710</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="8">
         <v>50</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12">
         <v>1400</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12">
         <v>72</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -70248,4 +70189,183 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE5DDDC2-842B-43D3-B52D-06647F226661}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="2" spans="1:3" ht="36" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <f>COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>690</v>
+      </c>
+      <c r="C3" s="1">
+        <f>COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$H:$H,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>0.63623188405797104</v>
+      </c>
+      <c r="C4" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$H:$H,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>0.72394366197183102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$I:$I,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>0.25072463768115943</v>
+      </c>
+      <c r="C5" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$I:$I,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>0.29014084507042254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$J:$J,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>0.15652173913043479</v>
+      </c>
+      <c r="C6" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$J:$J,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>0.21126760563380281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$K:$K,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>3.1884057971014491E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$K:$K,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>7.0422535211267609E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Control")/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>51.974318840579706</v>
+      </c>
+      <c r="C8" s="1">
+        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Treatment")/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>54.254521126760551</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Control")/COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$K:$K,1)</f>
+        <v>1630.1036363636363</v>
+      </c>
+      <c r="C9" s="1">
+        <f>SUMIFS([1]experiment_data!$L:$L,[1]experiment_data!$C:$C,"Treatment")/COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$K:$K,1)</f>
+        <v>770.41419999999982</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$N:$N,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$N:$N,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>4.2253521126760559E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Control",[1]experiment_data!$M:$M,1)/COUNTIF([1]experiment_data!$C:$C,"Control")</f>
+        <v>9.2753623188405798E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <f>COUNTIFS([1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$M:$M,1)/COUNTIF([1]experiment_data!$C:$C,"Treatment")</f>
+        <v>0.16056338028169015</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <f>AVERAGEIFS([1]experiment_data!$P:$P,[1]experiment_data!$C:$C,"Control")</f>
+        <v>57.029532163742729</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGEIFS([1]experiment_data!$P:$P,[1]experiment_data!$C:$C,"Treatment")</f>
+        <v>62.940028490028489</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <f>AVERAGEIFS([1]experiment_data!$O:$O,[1]experiment_data!$C:$C,"Control",[1]experiment_data!$K:$K,1)</f>
+        <v>8.8636363636363633</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGEIFS([1]experiment_data!$O:$O,[1]experiment_data!$C:$C,"Treatment",[1]experiment_data!$K:$K,1)</f>
+        <v>6.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>